--- a/artfynd/A 42442-2024 artfynd.xlsx
+++ b/artfynd/A 42442-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106979947</v>
+        <v>119048437</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2051</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sågdammen, Nrk</t>
+          <t>Sarvebäcken, Toberget, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520512.6529521808</v>
+        <v>520366</v>
       </c>
       <c r="R2" t="n">
-        <v>6540033.190206904</v>
+        <v>6539905</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-02-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-02-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,72 +772,67 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Ernie Haglund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum, Amanda Linderum</t>
+          <t>Ernie Haglund, Sabrina Mitra</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106979909</v>
+        <v>129728749</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sågdammen, Nrk</t>
+          <t>Jonse mosse, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520497.8361958564</v>
+        <v>520350</v>
       </c>
       <c r="R3" t="n">
-        <v>6540101.632309797</v>
+        <v>6539870</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,22 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-25</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-25</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,6 +896,354 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>106979909</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sågdammen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>520498</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6540102</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-02-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-02-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum, Amanda Linderum</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>107956511</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jonse mosse, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>520462</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6540073</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-04-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-04-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>106979947</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sågdammen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>520513</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6540033</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-02-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-02-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum, Amanda Linderum</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42442-2024 artfynd.xlsx
+++ b/artfynd/A 42442-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119048437</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728749</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106979909</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107956511</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,8 +1269,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106979947</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>